--- a/templates/ADJ_template.xlsx
+++ b/templates/ADJ_template.xlsx
@@ -35,6 +35,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="200" formatCode="dd/mm/yyyy"/>
+  </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -162,7 +165,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -192,10 +195,10 @@
     <xf numFmtId="1" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -208,7 +211,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -274,6 +277,13 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="200" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="200" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
